--- a/data/trans_orig/P33B2_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P33B2_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que se despierta durante la noche y tiene dificultad en volver a dormirse en 2023</t>
+          <t>Población según la frecuencia con la que se despierta durante la noche y tiene dificultad en volver a dormirse en 2023 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15307</t>
+          <t>15419</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33960</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14213</t>
+          <t>14447</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28279</t>
+          <t>28189</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33785</t>
+          <t>34111</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56716</t>
+          <t>56392</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26412</t>
+          <t>27887</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51028</t>
+          <t>52127</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35693</t>
+          <t>35690</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54533</t>
+          <t>56502</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>66490</t>
+          <t>68112</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>96890</t>
+          <t>99747</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>79251</t>
+          <t>79492</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>115681</t>
+          <t>116002</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>90230</t>
+          <t>90168</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>118452</t>
+          <t>119431</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>177479</t>
+          <t>177404</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>222758</t>
+          <t>224365</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,55%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>325980</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>370415</t>
+          <t>369273</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>261501</t>
+          <t>260644</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>294875</t>
+          <t>294397</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>600398</t>
+          <t>598864</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>655050</t>
+          <t>654075</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,66%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15505</t>
+          <t>16132</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32613</t>
+          <t>34091</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21905</t>
+          <t>22250</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39035</t>
+          <t>39049</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>42133</t>
+          <t>42603</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>66451</t>
+          <t>67111</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22302</t>
+          <t>22279</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45604</t>
+          <t>45056</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30480</t>
+          <t>30863</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50807</t>
+          <t>49655</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57873</t>
+          <t>59228</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89098</t>
+          <t>87101</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80285</t>
+          <t>81128</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>113080</t>
+          <t>114657</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79680</t>
+          <t>78969</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>108221</t>
+          <t>108057</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>166323</t>
+          <t>165024</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>211148</t>
+          <t>211572</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,34%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>280292</t>
+          <t>278614</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>320458</t>
+          <t>320115</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>203631</t>
+          <t>203429</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>235084</t>
+          <t>236206</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>496561</t>
+          <t>491812</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>548630</t>
+          <t>545586</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,36%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>15139</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70944</t>
+          <t>71582</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12386</t>
+          <t>12827</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24619</t>
+          <t>24389</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24482</t>
+          <t>25023</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>89654</t>
+          <t>88638</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11813</t>
+          <t>14104</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>64035</t>
+          <t>65868</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19531</t>
+          <t>19384</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36060</t>
+          <t>35658</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>24010</t>
+          <t>28130</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>96922</t>
+          <t>95932</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>33565</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>140320</t>
+          <t>141995</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31811</t>
+          <t>30292</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48148</t>
+          <t>47574</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>48883</t>
+          <t>53193</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>181315</t>
+          <t>180245</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,58%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>401694</t>
+          <t>399720</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>609618</t>
+          <t>597789</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73504</t>
+          <t>73649</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>94056</t>
+          <t>94895</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>477542</t>
+          <t>479629</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>738761</t>
+          <t>719800</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>86,19%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>64895</t>
+          <t>65743</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>97403</t>
+          <t>97524</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32941</t>
+          <t>37983</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>98185</t>
+          <t>94021</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>109620</t>
+          <t>103453</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>180569</t>
+          <t>177926</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>69651</t>
+          <t>68109</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>103802</t>
+          <t>102394</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>46505</t>
+          <t>50027</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>120565</t>
+          <t>121912</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>122910</t>
+          <t>126042</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>207778</t>
+          <t>204934</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>163512</t>
+          <t>162724</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>214356</t>
+          <t>210838</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>210739</t>
+          <t>211412</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>659629</t>
+          <t>617385</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>389055</t>
+          <t>389288</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976918</t>
+          <t>1009155</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>50,13%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>653323</t>
+          <t>652128</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>718184</t>
+          <t>711957</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>223518</t>
+          <t>262513</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>563177</t>
+          <t>562801</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>818546</t>
+          <t>761374</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1264518</t>
+          <t>1260141</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,6%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19154</t>
+          <t>20266</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>38675</t>
+          <t>40862</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>74477</t>
+          <t>73226</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>120060</t>
+          <t>118449</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>105481</t>
+          <t>98708</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>148912</t>
+          <t>147643</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38125</t>
+          <t>38293</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>65744</t>
+          <t>67671</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>92520</t>
+          <t>89045</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>143033</t>
+          <t>142767</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>136561</t>
+          <t>135028</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>194253</t>
+          <t>194676</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>77467</t>
+          <t>77194</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>111722</t>
+          <t>112796</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>128722</t>
+          <t>135589</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>208084</t>
+          <t>214531</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>222588</t>
+          <t>227011</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>306657</t>
+          <t>306916</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>279805</t>
+          <t>279897</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>323410</t>
+          <t>325544</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>382598</t>
+          <t>376667</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>549334</t>
+          <t>528084</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>692053</t>
+          <t>690614</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>855973</t>
+          <t>852305</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>64,91%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26718</t>
+          <t>24487</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>73679</t>
+          <t>74244</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>101389</t>
+          <t>102311</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>80549</t>
+          <t>80716</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>113719</t>
+          <t>116770</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>153</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>15371</t>
+          <t>9953</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>78930</t>
+          <t>76303</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>106700</t>
+          <t>105839</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>78857</t>
+          <t>78496</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>107846</t>
+          <t>109726</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7116</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>31590</t>
+          <t>29887</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>146032</t>
+          <t>145754</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>185268</t>
+          <t>183396</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>159475</t>
+          <t>158091</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>205299</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>196159</t>
+          <t>197734</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>226302</t>
+          <t>225477</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>395026</t>
+          <t>393996</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>443910</t>
+          <t>443521</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>598606</t>
+          <t>599311</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>663172</t>
+          <t>663838</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,26%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>157755</t>
+          <t>160794</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>234608</t>
+          <t>235670</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>262860</t>
+          <t>263759</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>363198</t>
+          <t>361794</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>460592</t>
+          <t>459361</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>582697</t>
+          <t>581843</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>189778</t>
+          <t>190041</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>281249</t>
+          <t>278819</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>330757</t>
+          <t>337486</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>453753</t>
+          <t>455641</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>574867</t>
+          <t>566813</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>715486</t>
+          <t>714146</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>427126</t>
+          <t>441172</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>634083</t>
+          <t>637995</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>782660</t>
+          <t>783890</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1461818</t>
+          <t>1495481</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1325377</t>
+          <t>1329063</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2060876</t>
+          <t>2095705</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>30,15%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2254868</t>
+          <t>2256823</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2605304</t>
+          <t>2583959</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1517936</t>
+          <t>1486115</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2024903</t>
+          <t>2030491</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3832214</t>
+          <t>3852688</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4499063</t>
+          <t>4491404</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,62%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33B2_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P33B2_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>23052</t>
+          <t>24681</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15419</t>
+          <t>16263</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33195</t>
+          <t>35795</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20403</t>
+          <t>22995</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14447</t>
+          <t>16769</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28189</t>
+          <t>32473</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>43455</t>
+          <t>47676</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34111</t>
+          <t>36841</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56392</t>
+          <t>61670</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37116</t>
+          <t>38689</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27887</t>
+          <t>28309</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52127</t>
+          <t>51954</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>44399</t>
+          <t>49272</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35690</t>
+          <t>39766</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56502</t>
+          <t>60859</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>81515</t>
+          <t>87962</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68112</t>
+          <t>73262</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>99747</t>
+          <t>106340</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>96241</t>
+          <t>106737</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>79492</t>
+          <t>87318</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>116002</t>
+          <t>126186</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>103971</t>
+          <t>117482</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>90168</t>
+          <t>101950</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>119431</t>
+          <t>134623</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>200212</t>
+          <t>224219</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>177404</t>
+          <t>199379</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>224365</t>
+          <t>248723</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,94%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>348803</t>
+          <t>380511</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>325980</t>
+          <t>357592</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>369273</t>
+          <t>402299</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>278694</t>
+          <t>298661</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>260644</t>
+          <t>279172</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>294397</t>
+          <t>316435</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>627497</t>
+          <t>679172</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>598864</t>
+          <t>646639</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>654075</t>
+          <t>706165</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>67,96%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23318</t>
+          <t>25189</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16132</t>
+          <t>17026</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34091</t>
+          <t>35490</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29746</t>
+          <t>34079</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22250</t>
+          <t>25883</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39049</t>
+          <t>44634</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>53064</t>
+          <t>59268</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>42603</t>
+          <t>47950</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>67111</t>
+          <t>74557</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>32287</t>
+          <t>32329</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22279</t>
+          <t>22497</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45056</t>
+          <t>46661</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>39720</t>
+          <t>45333</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30863</t>
+          <t>35536</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49655</t>
+          <t>55981</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>72007</t>
+          <t>77662</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59228</t>
+          <t>63887</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87101</t>
+          <t>95503</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>96311</t>
+          <t>104924</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81128</t>
+          <t>89083</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>114657</t>
+          <t>125930</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>92950</t>
+          <t>101602</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78969</t>
+          <t>86950</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>108057</t>
+          <t>116642</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>189261</t>
+          <t>206526</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>165024</t>
+          <t>181967</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>211572</t>
+          <t>230272</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>300298</t>
+          <t>320770</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>278614</t>
+          <t>297320</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>320115</t>
+          <t>340694</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>220163</t>
+          <t>242129</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>203429</t>
+          <t>224141</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>236206</t>
+          <t>259760</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>520461</t>
+          <t>562899</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>491812</t>
+          <t>534057</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>545586</t>
+          <t>590531</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,15%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>41579</t>
+          <t>45204</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15139</t>
+          <t>34696</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71582</t>
+          <t>57899</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>17858</t>
+          <t>20286</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12827</t>
+          <t>14197</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24389</t>
+          <t>27654</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>59438</t>
+          <t>65490</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25023</t>
+          <t>51893</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>88638</t>
+          <t>81372</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37621</t>
+          <t>40316</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>28053</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>65868</t>
+          <t>53339</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26476</t>
+          <t>29743</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19384</t>
+          <t>21615</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>35658</t>
+          <t>39843</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>64097</t>
+          <t>70059</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>28130</t>
+          <t>56344</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>95932</t>
+          <t>85861</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>85114</t>
+          <t>94073</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33565</t>
+          <t>79755</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>141995</t>
+          <t>110637</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>41924</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30292</t>
+          <t>33861</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47574</t>
+          <t>51839</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>123809</t>
+          <t>135997</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53193</t>
+          <t>118149</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>180245</t>
+          <t>156474</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>23,74%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>503949</t>
+          <t>292020</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>399720</t>
+          <t>272011</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>597789</t>
+          <t>314744</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>83881</t>
+          <t>95544</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73649</t>
+          <t>85507</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>94895</t>
+          <t>107100</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>587831</t>
+          <t>387563</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>479629</t>
+          <t>362070</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>719800</t>
+          <t>412411</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>62,57%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>80076</t>
+          <t>90463</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>65743</t>
+          <t>73837</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>97524</t>
+          <t>109082</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>71197</t>
+          <t>80810</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37983</t>
+          <t>66188</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>94021</t>
+          <t>96984</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>151273</t>
+          <t>171274</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>103453</t>
+          <t>148227</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>177926</t>
+          <t>194843</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>85310</t>
+          <t>92698</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>68109</t>
+          <t>76442</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>102394</t>
+          <t>111856</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>90551</t>
+          <t>100175</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50027</t>
+          <t>85784</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>121912</t>
+          <t>116144</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>175860</t>
+          <t>192873</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>126042</t>
+          <t>171696</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>204934</t>
+          <t>216729</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>186918</t>
+          <t>209884</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>162724</t>
+          <t>184365</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>210838</t>
+          <t>236819</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>378360</t>
+          <t>197025</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>211412</t>
+          <t>179177</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>617385</t>
+          <t>221419</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>565278</t>
+          <t>406910</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>389288</t>
+          <t>374296</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1009155</t>
+          <t>441098</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>682515</t>
+          <t>738798</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>652128</t>
+          <t>706743</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>711957</t>
+          <t>773485</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>437986</t>
+          <t>483200</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>262513</t>
+          <t>458441</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>562801</t>
+          <t>507911</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1120501</t>
+          <t>1221998</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>761374</t>
+          <t>1182483</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1260141</t>
+          <t>1262670</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>63,35%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>28382</t>
+          <t>31392</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20266</t>
+          <t>22283</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40862</t>
+          <t>43389</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>98974</t>
+          <t>113428</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>73226</t>
+          <t>98004</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>118449</t>
+          <t>131841</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>127356</t>
+          <t>144821</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>98708</t>
+          <t>125786</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>147643</t>
+          <t>164939</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>49434</t>
+          <t>53468</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38293</t>
+          <t>39576</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>67671</t>
+          <t>69989</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>119890</t>
+          <t>131528</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>89045</t>
+          <t>114145</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>142767</t>
+          <t>148427</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>169324</t>
+          <t>184996</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>135028</t>
+          <t>163410</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>194676</t>
+          <t>209440</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>93206</t>
+          <t>111880</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>77194</t>
+          <t>92891</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>112796</t>
+          <t>134345</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>182339</t>
+          <t>202609</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>135589</t>
+          <t>183910</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>214531</t>
+          <t>224544</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>275546</t>
+          <t>314490</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>227011</t>
+          <t>286484</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>306916</t>
+          <t>344815</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>24,68%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>302993</t>
+          <t>370141</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>279897</t>
+          <t>345142</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>325544</t>
+          <t>395488</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>437794</t>
+          <t>382561</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>376667</t>
+          <t>356845</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>528084</t>
+          <t>405360</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>740787</t>
+          <t>752702</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>690614</t>
+          <t>722091</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>852305</t>
+          <t>793285</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>56,78%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1313012</t>
+          <t>1397009</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1313012</t>
+          <t>1397009</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1313012</t>
+          <t>1397009</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>8735</t>
+          <t>7944</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2435</t>
+          <t>2342</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24487</t>
+          <t>21912</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>86891</t>
+          <t>96413</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>74244</t>
+          <t>81501</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>102311</t>
+          <t>112840</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>95626</t>
+          <t>104357</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>80716</t>
+          <t>89184</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>116770</t>
+          <t>125852</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9953</t>
+          <t>10009</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>90828</t>
+          <t>101368</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>76303</t>
+          <t>86701</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>105839</t>
+          <t>116681</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>92799</t>
+          <t>104730</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>78496</t>
+          <t>89547</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>109726</t>
+          <t>122531</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>15365</t>
+          <t>15287</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7228</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>29887</t>
+          <t>29234</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>165016</t>
+          <t>179392</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>145754</t>
+          <t>161348</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>183396</t>
+          <t>203656</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,17 +3866,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>180381</t>
+          <t>194679</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>158091</t>
+          <t>171550</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>205299</t>
+          <t>218325</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>214437</t>
+          <t>210634</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>197734</t>
+          <t>194765</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>225477</t>
+          <t>221933</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>418636</t>
+          <t>467108</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>393996</t>
+          <t>441954</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>443521</t>
+          <t>496698</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>633073</t>
+          <t>677742</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>599311</t>
+          <t>642829</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>663838</t>
+          <t>710263</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>65,67%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>205143</t>
+          <t>224874</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>160794</t>
+          <t>197795</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>235670</t>
+          <t>255087</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>325069</t>
+          <t>368012</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>263759</t>
+          <t>337836</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>361794</t>
+          <t>399311</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>530212</t>
+          <t>592886</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>459361</t>
+          <t>552265</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>581843</t>
+          <t>634944</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>243738</t>
+          <t>260863</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>190041</t>
+          <t>232227</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>278819</t>
+          <t>293330</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>411864</t>
+          <t>457420</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>337486</t>
+          <t>423998</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>455641</t>
+          <t>489839</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>655602</t>
+          <t>718282</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>566813</t>
+          <t>673000</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>714146</t>
+          <t>761842</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>573154</t>
+          <t>642785</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>441172</t>
+          <t>594814</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>637995</t>
+          <t>691886</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>961331</t>
+          <t>840035</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>783890</t>
+          <t>798934</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1495481</t>
+          <t>884344</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1534486</t>
+          <t>1482821</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1329063</t>
+          <t>1415276</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2095705</t>
+          <t>1540257</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2352996</t>
+          <t>2312873</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2256823</t>
+          <t>2257388</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2583959</t>
+          <t>2372404</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1877154</t>
+          <t>1969203</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1486115</t>
+          <t>1912707</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2030491</t>
+          <t>2020993</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>4230149</t>
+          <t>4282076</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3852688</t>
+          <t>4208639</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4491404</t>
+          <t>4366446</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>61,71%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3375031</t>
+          <t>3441394</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3375031</t>
+          <t>3441394</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3375031</t>
+          <t>3441394</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3575418</t>
+          <t>3634670</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3575418</t>
+          <t>3634670</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3575418</t>
+          <t>3634670</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>6950449</t>
+          <t>7076064</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6950449</t>
+          <t>7076064</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6950449</t>
+          <t>7076064</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
